--- a/公积金反推收入-计算器.xlsx
+++ b/公积金反推收入-计算器.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAXGU\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAXGU\Desktop\financial_calculator-main\financial_calculator-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE6A9F01-1597-4074-8357-49A02C544033}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B948466-25BD-4F0C-B5B2-A3D52FF0D516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
   <si>
     <t>个税速算表（应纳税额：月）</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -35,10 +35,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>双公积金：元/月</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>公积金缴纳比例（个人）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -135,15 +131,23 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>一年实到手所有（包括双边的五险一金）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>一年双边五险一金</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>税后实到手工资（月，不包括五险一金）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>一年实际获得（包括双边的五险一金）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>一年实到手工资+一年公积金</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>双边公积金：元/月</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -151,7 +155,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -215,6 +219,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -344,7 +356,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -376,9 +388,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="4" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -398,6 +407,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -697,22 +712,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -742,22 +757,22 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -787,13 +802,13 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E5" s="1"/>
     </row>
@@ -812,7 +827,7 @@
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -820,15 +835,15 @@
         <v>13704</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B9" s="10"/>
-      <c r="F9" s="13">
+      <c r="F9" s="21">
         <f>IF($A$12-$B$2 &lt; 0.1,"超出上限",SUM($D$2,$D$4,$E$2,$E$4,$F$4)*12)</f>
         <v>357360</v>
       </c>
@@ -837,15 +852,15 @@
       <c r="A10" s="2">
         <v>2500</v>
       </c>
-      <c r="F10" s="14" t="s">
-        <v>28</v>
+      <c r="F10" s="13" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A11" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="14">
+        <v>6</v>
+      </c>
+      <c r="F11" s="20">
         <f>IF($A$12-$B$2 &lt; 0.1,"超出上限",SUM($D$2,$D$4,$E$2,$E$4)*12)</f>
         <v>159300</v>
       </c>
@@ -855,10 +870,17 @@
         <f>3*$A$8</f>
         <v>41112</v>
       </c>
+      <c r="F12" s="13" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A13" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
+      </c>
+      <c r="F13" s="20">
+        <f>12*$F$4+12*$A$2</f>
+        <v>262860</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -869,7 +891,7 @@
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.2">
@@ -879,7 +901,7 @@
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
@@ -889,7 +911,7 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.2">
@@ -900,7 +922,7 @@
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" s="8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.2">
@@ -910,26 +932,26 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="20" t="s">
+      <c r="A23" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="20"/>
-      <c r="C23" s="20"/>
-      <c r="D23" s="18" t="s">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B24" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="C24" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="19"/>
+      <c r="D24" s="18"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
@@ -941,7 +963,7 @@
       <c r="C25" s="7">
         <v>0</v>
       </c>
-      <c r="D25" s="15">
+      <c r="D25" s="14">
         <v>5000</v>
       </c>
     </row>
@@ -955,7 +977,7 @@
       <c r="C26" s="7">
         <v>0</v>
       </c>
-      <c r="D26" s="16"/>
+      <c r="D26" s="15"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
@@ -967,7 +989,7 @@
       <c r="C27" s="7">
         <v>210</v>
       </c>
-      <c r="D27" s="16"/>
+      <c r="D27" s="15"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
@@ -979,7 +1001,7 @@
       <c r="C28" s="7">
         <v>1410</v>
       </c>
-      <c r="D28" s="16"/>
+      <c r="D28" s="15"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
@@ -991,7 +1013,7 @@
       <c r="C29" s="7">
         <v>2660</v>
       </c>
-      <c r="D29" s="16"/>
+      <c r="D29" s="15"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
@@ -1003,7 +1025,7 @@
       <c r="C30" s="7">
         <v>4410</v>
       </c>
-      <c r="D30" s="16"/>
+      <c r="D30" s="15"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
@@ -1015,7 +1037,7 @@
       <c r="C31" s="7">
         <v>7160</v>
       </c>
-      <c r="D31" s="16"/>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
@@ -1027,14 +1049,14 @@
       <c r="C32" s="7">
         <v>15160</v>
       </c>
-      <c r="D32" s="17"/>
+      <c r="D32" s="16"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="20" t="s">
+      <c r="A51" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="20"/>
-      <c r="C51" s="20"/>
+      <c r="B51" s="19"/>
+      <c r="C51" s="19"/>
       <c r="D51" s="5" t="s">
         <v>1</v>
       </c>
@@ -1049,7 +1071,7 @@
       <c r="C52" s="7">
         <v>0</v>
       </c>
-      <c r="D52" s="15">
+      <c r="D52" s="14">
         <v>5000</v>
       </c>
     </row>
@@ -1063,7 +1085,7 @@
       <c r="C53" s="7">
         <v>0</v>
       </c>
-      <c r="D53" s="16"/>
+      <c r="D53" s="15"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
@@ -1075,7 +1097,7 @@
       <c r="C54" s="7">
         <v>210</v>
       </c>
-      <c r="D54" s="16"/>
+      <c r="D54" s="15"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
@@ -1087,7 +1109,7 @@
       <c r="C55" s="7">
         <v>1410</v>
       </c>
-      <c r="D55" s="16"/>
+      <c r="D55" s="15"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
@@ -1099,7 +1121,7 @@
       <c r="C56" s="7">
         <v>2660</v>
       </c>
-      <c r="D56" s="16"/>
+      <c r="D56" s="15"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
@@ -1111,7 +1133,7 @@
       <c r="C57" s="7">
         <v>4410</v>
       </c>
-      <c r="D57" s="16"/>
+      <c r="D57" s="15"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
@@ -1123,7 +1145,7 @@
       <c r="C58" s="7">
         <v>7160</v>
       </c>
-      <c r="D58" s="16"/>
+      <c r="D58" s="15"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
@@ -1135,7 +1157,7 @@
       <c r="C59" s="7">
         <v>15160</v>
       </c>
-      <c r="D59" s="17"/>
+      <c r="D59" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/公积金反推收入-计算器.xlsx
+++ b/公积金反推收入-计算器.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAXGU\Desktop\financial_calculator-main\financial_calculator-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAXGU\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B948466-25BD-4F0C-B5B2-A3D52FF0D516}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7445B90C-5BA9-4E53-BCDF-F31FE87939ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
   <si>
     <t>个税速算表（应纳税额：月）</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -148,6 +148,10 @@
   </si>
   <si>
     <t>双边公积金：元/月</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>税后实到手工资+公积金（月）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -391,6 +395,12 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -407,12 +417,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -811,6 +815,9 @@
         <v>20</v>
       </c>
       <c r="E5" s="1"/>
+      <c r="F5" s="8" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
@@ -824,6 +831,10 @@
         <f>$B$6*INDEX($B$25:$B$32, MATCH($B$6,$A$25:$A$32,1))-INDEX($C$25:$C$32, MATCH($B$6,$A$25:$A$32,1))</f>
         <v>1045</v>
       </c>
+      <c r="F6" s="2">
+        <f>$F$4+$A$2</f>
+        <v>21905</v>
+      </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
@@ -843,7 +854,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="10"/>
-      <c r="F9" s="21">
+      <c r="F9" s="15">
         <f>IF($A$12-$B$2 &lt; 0.1,"超出上限",SUM($D$2,$D$4,$E$2,$E$4,$F$4)*12)</f>
         <v>357360</v>
       </c>
@@ -860,7 +871,7 @@
       <c r="A11" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="20">
+      <c r="F11" s="14">
         <f>IF($A$12-$B$2 &lt; 0.1,"超出上限",SUM($D$2,$D$4,$E$2,$E$4)*12)</f>
         <v>159300</v>
       </c>
@@ -878,7 +889,7 @@
       <c r="A13" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="20">
+      <c r="F13" s="14">
         <f>12*$F$4+12*$A$2</f>
         <v>262860</v>
       </c>
@@ -932,12 +943,12 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="17" t="s">
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="19" t="s">
         <v>1</v>
       </c>
     </row>
@@ -951,7 +962,7 @@
       <c r="C24" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="18"/>
+      <c r="D24" s="20"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" s="6">
@@ -963,7 +974,7 @@
       <c r="C25" s="7">
         <v>0</v>
       </c>
-      <c r="D25" s="14">
+      <c r="D25" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -977,7 +988,7 @@
       <c r="C26" s="7">
         <v>0</v>
       </c>
-      <c r="D26" s="15"/>
+      <c r="D26" s="17"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" s="6">
@@ -989,7 +1000,7 @@
       <c r="C27" s="7">
         <v>210</v>
       </c>
-      <c r="D27" s="15"/>
+      <c r="D27" s="17"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" s="6">
@@ -1001,7 +1012,7 @@
       <c r="C28" s="7">
         <v>1410</v>
       </c>
-      <c r="D28" s="15"/>
+      <c r="D28" s="17"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" s="6">
@@ -1013,7 +1024,7 @@
       <c r="C29" s="7">
         <v>2660</v>
       </c>
-      <c r="D29" s="15"/>
+      <c r="D29" s="17"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" s="6">
@@ -1025,7 +1036,7 @@
       <c r="C30" s="7">
         <v>4410</v>
       </c>
-      <c r="D30" s="15"/>
+      <c r="D30" s="17"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" s="6">
@@ -1037,7 +1048,7 @@
       <c r="C31" s="7">
         <v>7160</v>
       </c>
-      <c r="D31" s="15"/>
+      <c r="D31" s="17"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" s="6">
@@ -1049,14 +1060,14 @@
       <c r="C32" s="7">
         <v>15160</v>
       </c>
-      <c r="D32" s="16"/>
+      <c r="D32" s="18"/>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="19" t="s">
+      <c r="A51" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B51" s="19"/>
-      <c r="C51" s="19"/>
+      <c r="B51" s="21"/>
+      <c r="C51" s="21"/>
       <c r="D51" s="5" t="s">
         <v>1</v>
       </c>
@@ -1071,7 +1082,7 @@
       <c r="C52" s="7">
         <v>0</v>
       </c>
-      <c r="D52" s="14">
+      <c r="D52" s="16">
         <v>5000</v>
       </c>
     </row>
@@ -1085,7 +1096,7 @@
       <c r="C53" s="7">
         <v>0</v>
       </c>
-      <c r="D53" s="15"/>
+      <c r="D53" s="17"/>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="6">
@@ -1097,7 +1108,7 @@
       <c r="C54" s="7">
         <v>210</v>
       </c>
-      <c r="D54" s="15"/>
+      <c r="D54" s="17"/>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="6">
@@ -1109,7 +1120,7 @@
       <c r="C55" s="7">
         <v>1410</v>
       </c>
-      <c r="D55" s="15"/>
+      <c r="D55" s="17"/>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="6">
@@ -1121,7 +1132,7 @@
       <c r="C56" s="7">
         <v>2660</v>
       </c>
-      <c r="D56" s="15"/>
+      <c r="D56" s="17"/>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="6">
@@ -1133,7 +1144,7 @@
       <c r="C57" s="7">
         <v>4410</v>
       </c>
-      <c r="D57" s="15"/>
+      <c r="D57" s="17"/>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="6">
@@ -1145,7 +1156,7 @@
       <c r="C58" s="7">
         <v>7160</v>
       </c>
-      <c r="D58" s="15"/>
+      <c r="D58" s="17"/>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="6">
@@ -1157,7 +1168,7 @@
       <c r="C59" s="7">
         <v>15160</v>
       </c>
-      <c r="D59" s="16"/>
+      <c r="D59" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/公积金反推收入-计算器.xlsx
+++ b/公积金反推收入-计算器.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MAXGU\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7445B90C-5BA9-4E53-BCDF-F31FE87939ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{321C2EC9-6E8B-4928-8D6B-CC615749A295}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>个税速算表（应纳税额：月）</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -95,10 +95,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>应纳税额（月）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>公积金缴纳基数（月）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -107,10 +103,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>个税（月）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>个人公积金（月）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -139,10 +131,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>一年实际获得（包括双边的五险一金）</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>一年实到手工资+一年公积金</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -152,6 +140,19 @@
   </si>
   <si>
     <t>税后实到手工资+公积金（月）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>应纳税所得额（月）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>月均个税（全年平均）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>一年实际获得（包括双边的五险一金）
+又叫：税后综合用工价值（含单位五险一金）</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -360,7 +361,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -374,9 +375,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -391,7 +389,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -418,6 +415,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -703,7 +703,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F59"/>
+  <dimension ref="A1:F32"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="29.125" customWidth="1"/>
@@ -711,27 +711,27 @@
     <col min="3" max="3" width="28.625" customWidth="1"/>
     <col min="4" max="4" width="18.875" customWidth="1"/>
     <col min="5" max="5" width="18.5" customWidth="1"/>
-    <col min="6" max="6" width="35.875" customWidth="1"/>
+    <col min="6" max="6" width="42.875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B1" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C1" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="D1" s="8" t="s">
+      <c r="C1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>23</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -763,20 +763,20 @@
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" s="8" t="s">
+      <c r="C3" s="7" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E3" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>27</v>
+      <c r="F3" s="7" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.2">
@@ -801,22 +801,22 @@
       </c>
       <c r="F4" s="2">
         <f>IF($A$12-$B$2 &lt; 0.1,"超出上限", $F$2-$D$2-$D$4-$C$6)</f>
-        <v>16505</v>
+        <v>16450</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>20</v>
+      <c r="B5" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>30</v>
       </c>
       <c r="E5" s="1"/>
-      <c r="F5" s="8" t="s">
-        <v>31</v>
+      <c r="F5" s="7" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -824,16 +824,19 @@
         <v>0.12</v>
       </c>
       <c r="B6" s="2">
-        <f>$F$2-$D$2-$D$4-$D$25</f>
+        <f>MAX(0,$F$2-$D$2-$D$4-$D$25)</f>
         <v>12550</v>
       </c>
       <c r="C6" s="2">
-        <f>$B$6*INDEX($B$25:$B$32, MATCH($B$6,$A$25:$A$32,1))-INDEX($C$25:$C$32, MATCH($B$6,$A$25:$A$32,1))</f>
-        <v>1045</v>
+        <f>IF($B$6&lt;=0,0,
+ $B$6*INDEX($B$25:$B$31,MATCH($B$6,$A$25:$A$31,1))
+ -INDEX($C$25:$C$31,MATCH($B$6,$A$25:$A$31,1))
+)</f>
+        <v>1100</v>
       </c>
       <c r="F6" s="2">
         <f>$F$4+$A$2</f>
-        <v>21905</v>
+        <v>21850</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -841,37 +844,37 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="9">
+    <row r="8" spans="1:6" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="A8" s="8">
         <v>13704</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>28</v>
+      <c r="F8" s="20" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="10"/>
-      <c r="F9" s="15">
+      <c r="B9" s="9"/>
+      <c r="F9" s="13">
         <f>IF($A$12-$B$2 &lt; 0.1,"超出上限",SUM($D$2,$D$4,$E$2,$E$4,$F$4)*12)</f>
-        <v>357360</v>
+        <v>356700</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A10" s="2">
         <v>2500</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>26</v>
+      <c r="F10" s="11" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="8" t="s">
+      <c r="A11" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F11" s="14">
+      <c r="F11" s="12">
         <f>IF($A$12-$B$2 &lt; 0.1,"超出上限",SUM($D$2,$D$4,$E$2,$E$4)*12)</f>
         <v>159300</v>
       </c>
@@ -881,17 +884,17 @@
         <f>3*$A$8</f>
         <v>41112</v>
       </c>
-      <c r="F12" s="13" t="s">
-        <v>29</v>
+      <c r="F12" s="11" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="F13" s="14">
+      <c r="F13" s="12">
         <f>12*$F$4+12*$A$2</f>
-        <v>262860</v>
+        <v>262200</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -921,7 +924,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="8" t="s">
+      <c r="A19" s="7" t="s">
         <v>10</v>
       </c>
     </row>
@@ -932,7 +935,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A21" s="8" t="s">
+      <c r="A21" s="7" t="s">
         <v>11</v>
       </c>
     </row>
@@ -943,240 +946,124 @@
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B23" s="21"/>
-      <c r="C23" s="21"/>
-      <c r="D23" s="19" t="s">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="17" t="s">
         <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A24" s="11" t="s">
+      <c r="A24" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="11" t="s">
+      <c r="B24" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C24" s="11" t="s">
+      <c r="C24" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="D24" s="20"/>
+      <c r="D24" s="18"/>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A25" s="6">
+      <c r="A25" s="5">
         <v>0</v>
       </c>
-      <c r="B25" s="7">
+      <c r="B25" s="6">
+        <v>0.03</v>
+      </c>
+      <c r="C25" s="6">
         <v>0</v>
       </c>
-      <c r="C25" s="7">
-        <v>0</v>
-      </c>
-      <c r="D25" s="16">
+      <c r="D25" s="14">
         <v>5000</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A26" s="6">
-        <v>5000</v>
-      </c>
-      <c r="B26" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0</v>
-      </c>
-      <c r="D26" s="17"/>
+      <c r="A26" s="5">
+        <v>3000</v>
+      </c>
+      <c r="B26" s="6">
+        <v>0.1</v>
+      </c>
+      <c r="C26" s="6">
+        <v>210</v>
+      </c>
+      <c r="D26" s="15"/>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A27" s="6">
-        <v>8000</v>
-      </c>
-      <c r="B27" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="C27" s="7">
-        <v>210</v>
-      </c>
-      <c r="D27" s="17"/>
+      <c r="A27" s="5">
+        <v>12000</v>
+      </c>
+      <c r="B27" s="6">
+        <v>0.2</v>
+      </c>
+      <c r="C27" s="6">
+        <v>1410</v>
+      </c>
+      <c r="D27" s="15"/>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A28" s="6">
-        <v>17000</v>
-      </c>
-      <c r="B28" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="C28" s="7">
-        <v>1410</v>
-      </c>
-      <c r="D28" s="17"/>
+      <c r="A28" s="5">
+        <v>25000</v>
+      </c>
+      <c r="B28" s="6">
+        <v>0.25</v>
+      </c>
+      <c r="C28" s="6">
+        <v>2660</v>
+      </c>
+      <c r="D28" s="15"/>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A29" s="6">
-        <v>30000</v>
-      </c>
-      <c r="B29" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="C29" s="7">
-        <v>2660</v>
-      </c>
-      <c r="D29" s="17"/>
+      <c r="A29" s="5">
+        <v>35000</v>
+      </c>
+      <c r="B29" s="6">
+        <v>0.3</v>
+      </c>
+      <c r="C29" s="6">
+        <v>4410</v>
+      </c>
+      <c r="D29" s="15"/>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A30" s="6">
-        <v>40000</v>
-      </c>
-      <c r="B30" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="C30" s="7">
-        <v>4410</v>
-      </c>
-      <c r="D30" s="17"/>
+      <c r="A30" s="5">
+        <v>55000</v>
+      </c>
+      <c r="B30" s="6">
+        <v>0.35</v>
+      </c>
+      <c r="C30" s="6">
+        <v>7160</v>
+      </c>
+      <c r="D30" s="15"/>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A31" s="6">
-        <v>60000</v>
-      </c>
-      <c r="B31" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="C31" s="7">
-        <v>7160</v>
-      </c>
-      <c r="D31" s="17"/>
+      <c r="A31" s="5">
+        <v>80000</v>
+      </c>
+      <c r="B31" s="6">
+        <v>0.45</v>
+      </c>
+      <c r="C31" s="6">
+        <v>15160</v>
+      </c>
+      <c r="D31" s="15"/>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A32" s="6">
-        <v>85000</v>
-      </c>
-      <c r="B32" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="C32" s="7">
-        <v>15160</v>
-      </c>
-      <c r="D32" s="18"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A51" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="B51" s="21"/>
-      <c r="C51" s="21"/>
-      <c r="D51" s="5" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A52" s="6">
-        <v>0</v>
-      </c>
-      <c r="B52" s="7">
-        <v>0</v>
-      </c>
-      <c r="C52" s="7">
-        <v>0</v>
-      </c>
-      <c r="D52" s="16">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A53" s="6">
-        <v>5000</v>
-      </c>
-      <c r="B53" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="C53" s="7">
-        <v>0</v>
-      </c>
-      <c r="D53" s="17"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A54" s="6">
-        <v>8000</v>
-      </c>
-      <c r="B54" s="7">
-        <v>0.1</v>
-      </c>
-      <c r="C54" s="7">
-        <v>210</v>
-      </c>
-      <c r="D54" s="17"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A55" s="6">
-        <v>17000</v>
-      </c>
-      <c r="B55" s="7">
-        <v>0.2</v>
-      </c>
-      <c r="C55" s="7">
-        <v>1410</v>
-      </c>
-      <c r="D55" s="17"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A56" s="6">
-        <v>30000</v>
-      </c>
-      <c r="B56" s="7">
-        <v>0.25</v>
-      </c>
-      <c r="C56" s="7">
-        <v>2660</v>
-      </c>
-      <c r="D56" s="17"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A57" s="6">
-        <v>40000</v>
-      </c>
-      <c r="B57" s="7">
-        <v>0.3</v>
-      </c>
-      <c r="C57" s="7">
-        <v>4410</v>
-      </c>
-      <c r="D57" s="17"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A58" s="6">
-        <v>60000</v>
-      </c>
-      <c r="B58" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="C58" s="7">
-        <v>7160</v>
-      </c>
-      <c r="D58" s="17"/>
-    </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A59" s="6">
-        <v>85000</v>
-      </c>
-      <c r="B59" s="7">
-        <v>0.45</v>
-      </c>
-      <c r="C59" s="7">
-        <v>15160</v>
-      </c>
-      <c r="D59" s="18"/>
+      <c r="A32" s="5"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="3">
     <mergeCell ref="D25:D32"/>
     <mergeCell ref="D23:D24"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A51:C51"/>
-    <mergeCell ref="D52:D59"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
